--- a/content/site.xlsx
+++ b/content/site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofc-my.sharepoint.com/personal/pierre_khalil_ucalgary_ca/Documents/Personal/Personal stuff/Raspberry pi stuff/stmina-hymns-school/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26297944-2E84-4E38-9EA2-B24D812188F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{26297944-2E84-4E38-9EA2-B24D812188F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{170C4B6A-7D22-4CFB-B453-C0426D5308FD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -312,9 +312,6 @@
     <t>Tai-Shori</t>
   </si>
   <si>
-    <t>https://on.soundcloud.com/tonXC1bVbphA9nr5EC</t>
-  </si>
-  <si>
     <t>This is the censer of pure gold bearing the aroma, in the hands of Aaron the priest, offering up incense on the altar.</t>
   </si>
   <si>
@@ -322,6 +319,9 @@
   </si>
   <si>
     <t>Tay-shory ennob enka-tharos etfai kha pi-aro-mata, etkhen nen-jeeg en-A-aron pi-oweeb eftale oo-estoi-nofi e-epshoi ejen pima en-ersho-oshi.</t>
+  </si>
+  <si>
+    <t>https://soundcloud.com/coptic-hymns-library/13tai-shori?utm_source=clipboard&amp;utm_medium=text&amp;utm_campaign=social_sharing</t>
   </si>
 </sst>
 </file>
@@ -433,17 +433,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="22" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,6 +485,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -744,14 +748,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.15" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3"/>
@@ -930,14 +934,14 @@
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
@@ -1041,7 +1045,7 @@
       <c r="A5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="8">
         <v>46235.109027777777</v>
       </c>
     </row>
@@ -1260,7 +1264,7 @@
       <c r="A3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
@@ -1401,7 +1405,7 @@
         <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2">
         <v>10</v>
@@ -1475,13 +1479,13 @@
         <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
